--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.111.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.111.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.111.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.111.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.111.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.111.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0111.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0111.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: are subpo Ã¦ n Ã¦ ed in the same manner as at the hearing,</t>
+          <t>L76: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F :: 福 4</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE MASTERâ€™S OFFICE.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]104</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]104</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: isolated marker/symbol line :: 104</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: %-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]104</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,22 +654,14 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L76: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER :: ç¦� 4</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L20: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: are subpÅ“nÃ¦d in the same manner as at the hearing,</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr"/>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: )</t>
+          <t>L50: isolated marker/symbol line :: %-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -702,17 +698,13 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: The manner of completing the Report is clearly enoughâ€˜</t>
-        </is>
-      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: /</t>
+          <t>L91: isolated marker/symbol line :: )</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -734,12 +726,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -753,7 +745,11 @@
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L93: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -929,12 +925,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -973,7 +969,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1012,7 +1008,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
